--- a/testdata/LeaveAdjustmentData.xlsx
+++ b/testdata/LeaveAdjustmentData.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="20490" windowHeight="7620"/>
+    <workbookView windowWidth="19200" windowHeight="6200"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1224,7 +1224,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:E2"/>
-  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15" outlineLevelRow="1" outlineLevelCol="4"/>
+  <sheetFormatPr defaultColWidth="9.14545454545454" defaultRowHeight="14.5" outlineLevelRow="1" outlineLevelCol="4"/>
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="1" t="s">
@@ -1254,10 +1254,10 @@
         <v>1</v>
       </c>
       <c r="D2" s="3">
-        <v>45776</v>
+        <v>45990</v>
       </c>
       <c r="E2" s="3">
-        <v>45776</v>
+        <v>45990</v>
       </c>
     </row>
   </sheetData>

--- a/testdata/LeaveAdjustmentData.xlsx
+++ b/testdata/LeaveAdjustmentData.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="6200"/>
+    <workbookView windowWidth="19200" windowHeight="6920"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="9">
   <si>
     <t>Emp. ID</t>
   </si>
@@ -49,6 +49,12 @@
   <si>
     <t>CL</t>
   </si>
+  <si>
+    <t>17-Oct-2025</t>
+  </si>
+  <si>
+    <t>2025-Oct-17</t>
+  </si>
 </sst>
 </file>
 
@@ -59,7 +65,7 @@
     <numFmt numFmtId="177" formatCode="_ &quot;₹&quot;* #,##0.00_ ;_ &quot;₹&quot;* \-#,##0.00_ ;_ &quot;₹&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="179" formatCode="_ &quot;₹&quot;* #,##0_ ;_ &quot;₹&quot;* \-#,##0_ ;_ &quot;₹&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="180" formatCode="dd/mmm/yy"/>
+    <numFmt numFmtId="180" formatCode="[$-409]d/mmm/yyyy;@"/>
   </numFmts>
   <fonts count="22">
     <font>
@@ -689,7 +695,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="180" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="180" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -698,7 +706,7 @@
     <cellStyle name="Percent" xfId="3" builtinId="5"/>
     <cellStyle name="Comma [0]" xfId="4" builtinId="6"/>
     <cellStyle name="Currency [0]" xfId="5" builtinId="7"/>
-    <cellStyle name="Hyperlink" xfId="6" builtinId="8"/>
+    <cellStyle name="Link" xfId="6" builtinId="8"/>
     <cellStyle name="Followed Hyperlink" xfId="7" builtinId="9"/>
     <cellStyle name="Note" xfId="8" builtinId="10"/>
     <cellStyle name="Warning Text" xfId="9" builtinId="11"/>
@@ -1225,6 +1233,10 @@
   <sheetPr/>
   <dimension ref="A1:E2"/>
   <sheetFormatPr defaultColWidth="9.14545454545454" defaultRowHeight="14.5" outlineLevelRow="1" outlineLevelCol="4"/>
+  <cols>
+    <col min="4" max="4" customWidth="true" width="12.0909090909091"/>
+    <col min="5" max="5" customWidth="true" width="11.2727272727273"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="1" t="s">
@@ -1253,11 +1265,11 @@
       <c r="C2" s="2">
         <v>1</v>
       </c>
-      <c r="D2" s="3">
-        <v>45990</v>
+      <c r="D2" t="s" s="0">
+        <v>8</v>
       </c>
-      <c r="E2" s="3">
-        <v>45990</v>
+      <c r="E2" t="s" s="0">
+        <v>8</v>
       </c>
     </row>
   </sheetData>

--- a/testdata/LeaveAdjustmentData.xlsx
+++ b/testdata/LeaveAdjustmentData.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="6920"/>
+    <workbookView windowWidth="13860" windowHeight="6200"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="8">
   <si>
     <t>Emp. ID</t>
   </si>
@@ -50,22 +50,18 @@
     <t>CL</t>
   </si>
   <si>
-    <t>17-Oct-2025</t>
-  </si>
-  <si>
-    <t>2025-Oct-17</t>
+    <t>2025-Nov-19</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="5">
+  <numFmts count="4">
     <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_ &quot;₹&quot;* #,##0.00_ ;_ &quot;₹&quot;* \-#,##0.00_ ;_ &quot;₹&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="179" formatCode="_ &quot;₹&quot;* #,##0_ ;_ &quot;₹&quot;* \-#,##0_ ;_ &quot;₹&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="180" formatCode="[$-409]d/mmm/yyyy;@"/>
   </numFmts>
   <fonts count="22">
     <font>
@@ -687,7 +683,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -695,9 +691,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="180" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
-      <alignment vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1234,8 +1227,8 @@
   <dimension ref="A1:E2"/>
   <sheetFormatPr defaultColWidth="9.14545454545454" defaultRowHeight="14.5" outlineLevelRow="1" outlineLevelCol="4"/>
   <cols>
-    <col min="4" max="4" customWidth="true" width="12.0909090909091"/>
-    <col min="5" max="5" customWidth="true" width="11.2727272727273"/>
+    <col min="4" max="4" width="12.0909090909091" customWidth="1"/>
+    <col min="5" max="5" width="11.2727272727273" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -1265,11 +1258,11 @@
       <c r="C2" s="2">
         <v>1</v>
       </c>
-      <c r="D2" t="s" s="0">
-        <v>8</v>
+      <c r="D2" t="s">
+        <v>7</v>
       </c>
-      <c r="E2" t="s" s="0">
-        <v>8</v>
+      <c r="E2" t="s">
+        <v>7</v>
       </c>
     </row>
   </sheetData>

--- a/testdata/LeaveAdjustmentData.xlsx
+++ b/testdata/LeaveAdjustmentData.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="9">
   <si>
     <t>Emp. ID</t>
   </si>
@@ -51,6 +51,9 @@
   </si>
   <si>
     <t>2025-Nov-19</t>
+  </si>
+  <si>
+    <t>2025-Dec-04</t>
   </si>
 </sst>
 </file>
@@ -1227,8 +1230,8 @@
   <dimension ref="A1:E2"/>
   <sheetFormatPr defaultColWidth="9.14545454545454" defaultRowHeight="14.5" outlineLevelRow="1" outlineLevelCol="4"/>
   <cols>
-    <col min="4" max="4" width="12.0909090909091" customWidth="1"/>
-    <col min="5" max="5" width="11.2727272727273" customWidth="1"/>
+    <col min="4" max="4" customWidth="true" width="12.0909090909091"/>
+    <col min="5" max="5" customWidth="true" width="11.2727272727273"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -1258,11 +1261,11 @@
       <c r="C2" s="2">
         <v>1</v>
       </c>
-      <c r="D2" t="s">
-        <v>7</v>
+      <c r="D2" t="s" s="0">
+        <v>8</v>
       </c>
-      <c r="E2" t="s">
-        <v>7</v>
+      <c r="E2" t="s" s="0">
+        <v>8</v>
       </c>
     </row>
   </sheetData>

--- a/testdata/LeaveAdjustmentData.xlsx
+++ b/testdata/LeaveAdjustmentData.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="10">
   <si>
     <t>Emp. ID</t>
   </si>
@@ -54,6 +54,9 @@
   </si>
   <si>
     <t>2025-Dec-04</t>
+  </si>
+  <si>
+    <t>2026-Feb-05</t>
   </si>
 </sst>
 </file>
@@ -1262,10 +1265,10 @@
         <v>1</v>
       </c>
       <c r="D2" t="s" s="0">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E2" t="s" s="0">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>

--- a/testdata/LeaveAdjustmentData.xlsx
+++ b/testdata/LeaveAdjustmentData.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="11">
   <si>
     <t>Emp. ID</t>
   </si>
@@ -57,6 +57,9 @@
   </si>
   <si>
     <t>2026-Feb-05</t>
+  </si>
+  <si>
+    <t>2026-Apr-01</t>
   </si>
 </sst>
 </file>
@@ -1265,10 +1268,10 @@
         <v>1</v>
       </c>
       <c r="D2" t="s" s="0">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E2" t="s" s="0">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>

--- a/testdata/LeaveAdjustmentData.xlsx
+++ b/testdata/LeaveAdjustmentData.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="13">
   <si>
     <t>Emp. ID</t>
   </si>
@@ -60,6 +60,12 @@
   </si>
   <si>
     <t>2026-Apr-01</t>
+  </si>
+  <si>
+    <t>2026-Jul-08</t>
+  </si>
+  <si>
+    <t>2026-Jul-09</t>
   </si>
 </sst>
 </file>
@@ -1268,10 +1274,10 @@
         <v>1</v>
       </c>
       <c r="D2" t="s" s="0">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E2" t="s" s="0">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
   </sheetData>

--- a/testdata/LeaveAdjustmentData.xlsx
+++ b/testdata/LeaveAdjustmentData.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="13860" windowHeight="6200"/>
+    <workbookView windowWidth="19200" windowHeight="6920"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="8">
   <si>
     <t>Emp. ID</t>
   </si>
@@ -50,22 +50,7 @@
     <t>CL</t>
   </si>
   <si>
-    <t>2025-Nov-19</t>
-  </si>
-  <si>
-    <t>2025-Dec-04</t>
-  </si>
-  <si>
-    <t>2026-Feb-05</t>
-  </si>
-  <si>
-    <t>2026-Apr-01</t>
-  </si>
-  <si>
-    <t>2026-Jul-08</t>
-  </si>
-  <si>
-    <t>2026-Jul-09</t>
+    <t>2026-Sep-01</t>
   </si>
 </sst>
 </file>
@@ -719,7 +704,7 @@
     <cellStyle name="Note" xfId="8" builtinId="10"/>
     <cellStyle name="Warning Text" xfId="9" builtinId="11"/>
     <cellStyle name="Title" xfId="10" builtinId="15"/>
-    <cellStyle name="CExplanatory Text" xfId="11" builtinId="53"/>
+    <cellStyle name="Explanatory Text" xfId="11" builtinId="53"/>
     <cellStyle name="Heading 1" xfId="12" builtinId="16"/>
     <cellStyle name="Heading 2" xfId="13" builtinId="17"/>
     <cellStyle name="Heading 3" xfId="14" builtinId="18"/>
@@ -1274,10 +1259,10 @@
         <v>1</v>
       </c>
       <c r="D2" t="s" s="0">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="E2" t="s" s="0">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>

--- a/testdata/LeaveAdjustmentData.xlsx
+++ b/testdata/LeaveAdjustmentData.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="9">
   <si>
     <t>Emp. ID</t>
   </si>
@@ -51,6 +51,9 @@
   </si>
   <si>
     <t>2026-Sep-01</t>
+  </si>
+  <si>
+    <t>2026-Sep-28</t>
   </si>
 </sst>
 </file>
@@ -1259,10 +1262,10 @@
         <v>1</v>
       </c>
       <c r="D2" t="s" s="0">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E2" t="s" s="0">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
